--- a/Deployment_Automation/GVault_Deployment_Steps.xlsx
+++ b/Deployment_Automation/GVault_Deployment_Steps.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\z1xa7prdhomes.file.core.windows.net\prdhomes\Homes\awaghmode1\Documents\2025\AUTOMATION-DEPLOYMENT\approvers test\25GR3_VPK_MDL\Deployment_Automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\z1xa7prdhomes.file.core.windows.net\prdhomes\Homes\awaghmode1\Downloads\CICD pipeline automation test\25GR3_VPK_MDL\Deployment_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FC5101-D240-48F7-8C3E-BF5053D74042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB5EE4E-BC6F-4E32-B17A-034CA5E7BBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19320" windowHeight="8550" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="65">
   <si>
     <t>Steps</t>
   </si>
@@ -151,9 +151,6 @@
     <t>Approved</t>
   </si>
   <si>
-    <t>POC1 requires both</t>
-  </si>
-  <si>
     <t>Contigency</t>
   </si>
   <si>
@@ -169,9 +166,6 @@
     <t>Pending</t>
   </si>
   <si>
-    <t>Hold until sign-off</t>
-  </si>
-  <si>
     <t>qa1@gilead.com; qa2@gilead.com; qa3@gilead.com</t>
   </si>
   <si>
@@ -217,13 +211,13 @@
     <t>25GR2_Picklist_Dependency_Partner_Field.txt</t>
   </si>
   <si>
-    <t>ashwini.waghmode1@gilead.com; rahul.padole@gilead.com</t>
-  </si>
-  <si>
     <t>Monika.ChinthalaBabu@gilead.com</t>
   </si>
   <si>
     <t>Ashwini.Waghmode1@gilead.com</t>
+  </si>
+  <si>
+    <t>rahul.padole@gilead.com</t>
   </si>
 </sst>
 </file>
@@ -711,7 +705,7 @@
   <cols>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -787,7 +781,7 @@
         <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
         <v>27</v>
@@ -823,7 +817,7 @@
     <col min="3" max="3" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -861,20 +855,11 @@
       <c r="B2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -882,19 +867,13 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -905,16 +884,10 @@
         <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -922,25 +895,20 @@
         <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" display="carol@gilead.com" xr:uid="{0904F579-5F0E-4555-BDE3-E77BA463A11D}"/>
     <hyperlink ref="C4" r:id="rId2" display="seclead@gilead.com" xr:uid="{FEF8216C-789D-4835-9D7B-DFD8925D30E2}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{C105A4B5-5953-4B23-A022-D5F06CA6CD34}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -962,34 +930,34 @@
         <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -1009,13 +977,13 @@
         <v>41</v>
       </c>
       <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" t="s">
         <v>44</v>
       </c>
-      <c r="H2" t="s">
-        <v>45</v>
-      </c>
       <c r="J2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K2" t="s">
         <v>41</v>
@@ -1026,25 +994,25 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
         <v>45</v>
-      </c>
-      <c r="E3" t="s">
-        <v>46</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
       <c r="G3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
         <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1052,28 +1020,28 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
         <v>41</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Deployment_Automation/GVault_Deployment_Steps.xlsx
+++ b/Deployment_Automation/GVault_Deployment_Steps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\z1xa7prdhomes.file.core.windows.net\prdhomes\Homes\awaghmode1\Downloads\CICD pipeline automation test\25GR3_VPK_MDL\Deployment_Automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FB5EE4E-BC6F-4E32-B17A-034CA5E7BBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BEC38AC-05AD-4CAA-9AE6-534C3642B051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19320" windowHeight="8550" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -211,13 +211,13 @@
     <t>25GR2_Picklist_Dependency_Partner_Field.txt</t>
   </si>
   <si>
+    <t>ashwini.waghmode1@gilead.com; rahul.padole@gilead.com</t>
+  </si>
+  <si>
     <t>Monika.ChinthalaBabu@gilead.com</t>
   </si>
   <si>
     <t>Ashwini.Waghmode1@gilead.com</t>
-  </si>
-  <si>
-    <t>rahul.padole@gilead.com</t>
   </si>
 </sst>
 </file>
@@ -705,7 +705,7 @@
   <cols>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -817,7 +817,7 @@
     <col min="3" max="3" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -855,8 +855,8 @@
       <c r="B2" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>64</v>
+      <c r="C2" t="s">
+        <v>62</v>
       </c>
       <c r="D2" t="s">
         <v>44</v>
@@ -870,7 +870,7 @@
         <v>42</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
         <v>44</v>
@@ -884,7 +884,7 @@
         <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
         <v>44</v>
@@ -898,7 +898,7 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
         <v>40</v>
@@ -908,7 +908,6 @@
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" display="carol@gilead.com" xr:uid="{0904F579-5F0E-4555-BDE3-E77BA463A11D}"/>
     <hyperlink ref="C4" r:id="rId2" display="seclead@gilead.com" xr:uid="{FEF8216C-789D-4835-9D7B-DFD8925D30E2}"/>
-    <hyperlink ref="C2" r:id="rId3" xr:uid="{C105A4B5-5953-4B23-A022-D5F06CA6CD34}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
